--- a/Librairies/TEP_243-Altium_RLC_Librairie.xlsx
+++ b/Librairies/TEP_243-Altium_RLC_Librairie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lecegeplimoilou-my.sharepoint.com/personal/kevin_cotton_cegeplimoilou_ca/Documents/_Cours-TGE/Altium/243-TEP_Altium-Lib/Librairies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1191" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E4F7E99-0171-416A-8546-C9764C6CC03F}"/>
+  <xr:revisionPtr revIDLastSave="1405" documentId="13_ncr:1_{550D3E46-E4B6-4165-A45B-7D583CCE157E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9190E0A-28F7-471C-8965-575C10056F56}"/>
   <bookViews>
-    <workbookView xWindow="5460" yWindow="1596" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cap" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="459">
   <si>
     <t>Comment</t>
   </si>
@@ -972,24 +972,6 @@
     <t>C137341</t>
   </si>
   <si>
-    <t>Res 20R 1206</t>
-  </si>
-  <si>
-    <t>Res 270R 1206</t>
-  </si>
-  <si>
-    <t>Res 330R 1206</t>
-  </si>
-  <si>
-    <t>Res 470R 1206</t>
-  </si>
-  <si>
-    <t>Res 1k 1206</t>
-  </si>
-  <si>
-    <t>Res 1M 1206</t>
-  </si>
-  <si>
     <t>C114945</t>
   </si>
   <si>
@@ -1008,9 +990,6 @@
     <t>C137355</t>
   </si>
   <si>
-    <t>Res 1R 1206</t>
-  </si>
-  <si>
     <t>Code CEGEP</t>
   </si>
   <si>
@@ -1210,6 +1189,237 @@
   </si>
   <si>
     <t>R_2012[0805]</t>
+  </si>
+  <si>
+    <t>RES032</t>
+  </si>
+  <si>
+    <t>RES033</t>
+  </si>
+  <si>
+    <t>RES034</t>
+  </si>
+  <si>
+    <t>RES035</t>
+  </si>
+  <si>
+    <t>RES0483SMT</t>
+  </si>
+  <si>
+    <t>AV-P24, R14-H04</t>
+  </si>
+  <si>
+    <t>RES0485SMT</t>
+  </si>
+  <si>
+    <t>RES0486SMT</t>
+  </si>
+  <si>
+    <t>RES0487SMT</t>
+  </si>
+  <si>
+    <t>RES0488SMT</t>
+  </si>
+  <si>
+    <t>RES0489SMT</t>
+  </si>
+  <si>
+    <t>RES0490SMT</t>
+  </si>
+  <si>
+    <t>RES0491SMT</t>
+  </si>
+  <si>
+    <t>RES0492SMT</t>
+  </si>
+  <si>
+    <t>RES0493SMT</t>
+  </si>
+  <si>
+    <t>Res 4k 1% 0805</t>
+  </si>
+  <si>
+    <t>4k</t>
+  </si>
+  <si>
+    <t>RES036</t>
+  </si>
+  <si>
+    <t>RES037</t>
+  </si>
+  <si>
+    <t>RES038</t>
+  </si>
+  <si>
+    <t>RES039</t>
+  </si>
+  <si>
+    <t>RES040</t>
+  </si>
+  <si>
+    <t>RES041</t>
+  </si>
+  <si>
+    <t>RES042</t>
+  </si>
+  <si>
+    <t>Res 732R 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 6k04 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 576R 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 2R7 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 42k2 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 5k11 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 5k76 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 3k83 1% 0805</t>
+  </si>
+  <si>
+    <t>Res 1k21 1% 0805</t>
+  </si>
+  <si>
+    <t>732R</t>
+  </si>
+  <si>
+    <t>6k04</t>
+  </si>
+  <si>
+    <t>576R</t>
+  </si>
+  <si>
+    <t>2R7</t>
+  </si>
+  <si>
+    <t>42k2</t>
+  </si>
+  <si>
+    <t>5k11</t>
+  </si>
+  <si>
+    <t>5k76</t>
+  </si>
+  <si>
+    <t>3k83</t>
+  </si>
+  <si>
+    <t>1k21</t>
+  </si>
+  <si>
+    <t>CAP023</t>
+  </si>
+  <si>
+    <t>COND0137SM</t>
+  </si>
+  <si>
+    <t>AV-Q11--R14-J06</t>
+  </si>
+  <si>
+    <t>R13-C015-3</t>
+  </si>
+  <si>
+    <t>KCOND92SM</t>
+  </si>
+  <si>
+    <t>R13--C017-1</t>
+  </si>
+  <si>
+    <t>KCOND93SM</t>
+  </si>
+  <si>
+    <t>R13-C017-3</t>
+  </si>
+  <si>
+    <t>KCOND94SM</t>
+  </si>
+  <si>
+    <t>CAP CER 1uF 50V X?? 0603</t>
+  </si>
+  <si>
+    <t>CAP024</t>
+  </si>
+  <si>
+    <t>CAP025</t>
+  </si>
+  <si>
+    <t>CAP026</t>
+  </si>
+  <si>
+    <t>CAP CER 18pF 50V X?? 0603</t>
+  </si>
+  <si>
+    <t>CAP CER 10uF 10V X?? 0805</t>
+  </si>
+  <si>
+    <t>CAP CER 10uF 50V X7R 1206</t>
+  </si>
+  <si>
+    <t>18pF</t>
+  </si>
+  <si>
+    <t>RESI0045SMT</t>
+  </si>
+  <si>
+    <t>AV-P24--R14-J04</t>
+  </si>
+  <si>
+    <t>Res 150R 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 1k 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 1M 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 470R 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 330R 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 270R 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 20R 5% 1206</t>
+  </si>
+  <si>
+    <t>Res 1R 5% 1206</t>
+  </si>
+  <si>
+    <t>RESI0047SMT</t>
+  </si>
+  <si>
+    <t>Res 180R 5% 1206</t>
+  </si>
+  <si>
+    <t>180R</t>
+  </si>
+  <si>
+    <t>RES043</t>
+  </si>
+  <si>
+    <t>RES044</t>
+  </si>
+  <si>
+    <t>RES045</t>
+  </si>
+  <si>
+    <t>RESI0057SMT</t>
+  </si>
+  <si>
+    <t>RES046</t>
   </si>
 </sst>
 </file>
@@ -1278,7 +1488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1303,7 +1513,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1586,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -1610,10 +1819,10 @@
         <v>5</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>0</v>
@@ -1678,7 +1887,7 @@
         <v>69</v>
       </c>
       <c r="F2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="G2" t="s">
         <v>112</v>
@@ -1711,7 +1920,7 @@
         <v>46</v>
       </c>
       <c r="Q2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
@@ -1826,10 +2035,10 @@
         <v>257</v>
       </c>
       <c r="E5" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="F5" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="G5" t="s">
         <v>77</v>
@@ -2159,16 +2368,16 @@
         <v>164</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="E12" t="s">
         <v>114</v>
       </c>
       <c r="F12" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="G12" t="s">
         <v>165</v>
@@ -2201,7 +2410,7 @@
         <v>46</v>
       </c>
       <c r="Q12" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -2625,16 +2834,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>322</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E22" t="s">
         <v>329</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E22" t="s">
-        <v>336</v>
-      </c>
       <c r="F22" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="G22" t="s">
         <v>78</v>
@@ -2643,22 +2852,22 @@
         <v>147</v>
       </c>
       <c r="I22" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="J22" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="K22" t="s">
         <v>13</v>
       </c>
       <c r="L22" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="M22" t="s">
         <v>21</v>
       </c>
       <c r="N22" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="O22" t="s">
         <v>22</v>
@@ -2667,24 +2876,24 @@
         <v>46</v>
       </c>
       <c r="Q22" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E23" t="s">
         <v>114</v>
       </c>
       <c r="F23" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="G23" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>146</v>
@@ -2714,7 +2923,153 @@
         <v>46</v>
       </c>
       <c r="Q23" t="s">
-        <v>372</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>424</v>
+      </c>
+      <c r="B24" t="s">
+        <v>425</v>
+      </c>
+      <c r="C24" t="s">
+        <v>426</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" t="s">
+        <v>13</v>
+      </c>
+      <c r="L24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" t="s">
+        <v>21</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>434</v>
+      </c>
+      <c r="B25" t="s">
+        <v>428</v>
+      </c>
+      <c r="C25" t="s">
+        <v>429</v>
+      </c>
+      <c r="D25" t="s">
+        <v>433</v>
+      </c>
+      <c r="G25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I25" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" t="s">
+        <v>21</v>
+      </c>
+      <c r="N25" t="s">
+        <v>32</v>
+      </c>
+      <c r="O25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>435</v>
+      </c>
+      <c r="B26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C26" t="s">
+        <v>431</v>
+      </c>
+      <c r="D26" t="s">
+        <v>437</v>
+      </c>
+      <c r="G26" t="s">
+        <v>440</v>
+      </c>
+      <c r="I26" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N26" t="s">
+        <v>32</v>
+      </c>
+      <c r="O26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>436</v>
+      </c>
+      <c r="B27" t="s">
+        <v>432</v>
+      </c>
+      <c r="C27" t="s">
+        <v>427</v>
+      </c>
+      <c r="D27" t="s">
+        <v>438</v>
+      </c>
+      <c r="G27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" t="s">
+        <v>72</v>
+      </c>
+      <c r="K27" t="s">
+        <v>13</v>
+      </c>
+      <c r="L27" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" t="s">
+        <v>81</v>
+      </c>
+      <c r="O27" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2726,7 +3081,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0837104-CD0C-4055-94B3-0A98F94F86E8}">
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
@@ -2736,7 +3091,7 @@
     <col min="5" max="5" width="14.33203125" customWidth="1"/>
     <col min="6" max="6" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.77734375" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" customWidth="1"/>
+    <col min="11" max="11" width="6.44140625" customWidth="1"/>
     <col min="12" max="12" width="11.44140625" customWidth="1"/>
     <col min="13" max="13" width="11.77734375" customWidth="1"/>
     <col min="14" max="14" width="22.21875" style="2" customWidth="1"/>
@@ -2751,10 +3106,10 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
@@ -2913,7 +3268,7 @@
         <v>69</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -2946,7 +3301,7 @@
         <v>46</v>
       </c>
       <c r="Q4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
@@ -3104,7 +3459,7 @@
         <v>69</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G8" t="s">
         <v>67</v>
@@ -3137,7 +3492,7 @@
         <v>46</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -3207,7 +3562,7 @@
         <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="G10" t="s">
         <v>89</v>
@@ -3240,7 +3595,7 @@
         <v>46</v>
       </c>
       <c r="Q10" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="R10" t="s">
         <v>83</v>
@@ -3260,7 +3615,7 @@
         <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G11" t="s">
         <v>100</v>
@@ -3293,7 +3648,7 @@
         <v>46</v>
       </c>
       <c r="Q11" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
@@ -3310,7 +3665,7 @@
         <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G12" t="s">
         <v>101</v>
@@ -3343,7 +3698,7 @@
         <v>46</v>
       </c>
       <c r="Q12" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
@@ -3360,7 +3715,7 @@
         <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="G13" t="s">
         <v>102</v>
@@ -3393,7 +3748,7 @@
         <v>46</v>
       </c>
       <c r="Q13" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
@@ -3407,7 +3762,7 @@
         <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="G14" t="s">
         <v>161</v>
@@ -3440,7 +3795,7 @@
         <v>46</v>
       </c>
       <c r="Q14" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
@@ -3451,7 +3806,7 @@
         <v>278</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="E15" t="s">
         <v>69</v>
@@ -3704,19 +4059,19 @@
         <v>273</v>
       </c>
       <c r="D20" t="s">
-        <v>321</v>
+        <v>450</v>
       </c>
       <c r="E20" t="s">
         <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>274</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I20" t="s">
         <v>176</v>
@@ -3743,7 +4098,7 @@
         <v>46</v>
       </c>
       <c r="Q20" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
@@ -3754,7 +4109,7 @@
         <v>276</v>
       </c>
       <c r="D21" t="s">
-        <v>309</v>
+        <v>449</v>
       </c>
       <c r="E21" t="s">
         <v>69</v>
@@ -3766,7 +4121,7 @@
         <v>241</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I21" t="s">
         <v>176</v>
@@ -3804,7 +4159,7 @@
         <v>279</v>
       </c>
       <c r="D22" t="s">
-        <v>310</v>
+        <v>448</v>
       </c>
       <c r="E22" t="s">
         <v>69</v>
@@ -3816,7 +4171,7 @@
         <v>280</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I22" t="s">
         <v>176</v>
@@ -3854,7 +4209,7 @@
         <v>282</v>
       </c>
       <c r="D23" t="s">
-        <v>311</v>
+        <v>447</v>
       </c>
       <c r="E23" t="s">
         <v>69</v>
@@ -3866,7 +4221,7 @@
         <v>283</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I23" t="s">
         <v>176</v>
@@ -3904,7 +4259,7 @@
         <v>284</v>
       </c>
       <c r="D24" t="s">
-        <v>312</v>
+        <v>446</v>
       </c>
       <c r="E24" t="s">
         <v>69</v>
@@ -3916,7 +4271,7 @@
         <v>285</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
         <v>176</v>
@@ -3943,7 +4298,7 @@
         <v>46</v>
       </c>
       <c r="Q24" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.3">
@@ -3954,19 +4309,19 @@
         <v>289</v>
       </c>
       <c r="D25" t="s">
-        <v>313</v>
+        <v>444</v>
       </c>
       <c r="E25" t="s">
         <v>69</v>
       </c>
       <c r="F25" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>66</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I25" t="s">
         <v>176</v>
@@ -3993,7 +4348,7 @@
         <v>46</v>
       </c>
       <c r="Q25" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.3">
@@ -4004,7 +4359,7 @@
         <v>290</v>
       </c>
       <c r="D26" t="s">
-        <v>314</v>
+        <v>445</v>
       </c>
       <c r="E26" t="s">
         <v>69</v>
@@ -4016,7 +4371,7 @@
         <v>292</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I26" t="s">
         <v>176</v>
@@ -4043,7 +4398,7 @@
         <v>46</v>
       </c>
       <c r="Q26" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
@@ -4095,19 +4450,19 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="E28" t="s">
         <v>69</v>
       </c>
       <c r="F28" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="G28" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>149</v>
@@ -4137,24 +4492,24 @@
         <v>46</v>
       </c>
       <c r="Q28" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="E29" t="s">
         <v>69</v>
       </c>
       <c r="F29" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>149</v>
@@ -4184,24 +4539,24 @@
         <v>46</v>
       </c>
       <c r="Q29" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E30" t="s">
         <v>69</v>
       </c>
       <c r="F30" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>149</v>
@@ -4231,24 +4586,24 @@
         <v>46</v>
       </c>
       <c r="Q30" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>376</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>378</v>
+        <v>369</v>
+      </c>
+      <c r="D31" t="s">
+        <v>371</v>
       </c>
       <c r="E31" t="s">
         <v>69</v>
       </c>
       <c r="F31" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>149</v>
@@ -4278,33 +4633,33 @@
         <v>46</v>
       </c>
       <c r="Q31" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>377</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>379</v>
+        <v>370</v>
+      </c>
+      <c r="D32" t="s">
+        <v>372</v>
       </c>
       <c r="E32" t="s">
         <v>69</v>
       </c>
       <c r="F32" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>149</v>
       </c>
       <c r="I32" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="J32" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="K32" t="s">
         <v>13</v>
@@ -4316,7 +4671,7 @@
         <v>21</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="O32" t="s">
         <v>22</v>
@@ -4325,7 +4680,622 @@
         <v>46</v>
       </c>
       <c r="Q32" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>382</v>
+      </c>
+      <c r="B33" t="s">
+        <v>386</v>
+      </c>
+      <c r="C33" t="s">
+        <v>387</v>
+      </c>
+      <c r="D33" t="s">
+        <v>397</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" t="s">
+        <v>377</v>
+      </c>
+      <c r="J33" t="s">
+        <v>376</v>
+      </c>
+      <c r="K33" t="s">
+        <v>13</v>
+      </c>
+      <c r="L33" t="s">
+        <v>27</v>
+      </c>
+      <c r="M33" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>383</v>
+      </c>
+      <c r="B34" t="s">
+        <v>388</v>
+      </c>
+      <c r="C34" t="s">
+        <v>387</v>
+      </c>
+      <c r="D34" t="s">
+        <v>406</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" t="s">
+        <v>377</v>
+      </c>
+      <c r="J34" t="s">
+        <v>376</v>
+      </c>
+      <c r="K34" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" t="s">
+        <v>27</v>
+      </c>
+      <c r="M34" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>384</v>
+      </c>
+      <c r="B35" t="s">
+        <v>389</v>
+      </c>
+      <c r="C35" t="s">
+        <v>387</v>
+      </c>
+      <c r="D35" t="s">
+        <v>407</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" t="s">
+        <v>377</v>
+      </c>
+      <c r="J35" t="s">
+        <v>376</v>
+      </c>
+      <c r="K35" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" t="s">
+        <v>27</v>
+      </c>
+      <c r="M35" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>385</v>
+      </c>
+      <c r="B36" t="s">
+        <v>390</v>
+      </c>
+      <c r="C36" t="s">
+        <v>387</v>
+      </c>
+      <c r="D36" t="s">
+        <v>408</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" t="s">
+        <v>377</v>
+      </c>
+      <c r="J36" t="s">
+        <v>376</v>
+      </c>
+      <c r="K36" t="s">
+        <v>13</v>
+      </c>
+      <c r="L36" t="s">
+        <v>27</v>
+      </c>
+      <c r="M36" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O36" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>399</v>
+      </c>
+      <c r="B37" t="s">
+        <v>391</v>
+      </c>
+      <c r="C37" t="s">
+        <v>387</v>
+      </c>
+      <c r="D37" t="s">
+        <v>409</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I37" t="s">
+        <v>377</v>
+      </c>
+      <c r="J37" t="s">
+        <v>376</v>
+      </c>
+      <c r="K37" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" t="s">
+        <v>27</v>
+      </c>
+      <c r="M37" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>400</v>
+      </c>
+      <c r="B38" t="s">
+        <v>392</v>
+      </c>
+      <c r="C38" t="s">
+        <v>387</v>
+      </c>
+      <c r="D38" t="s">
+        <v>410</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I38" t="s">
+        <v>377</v>
+      </c>
+      <c r="J38" t="s">
+        <v>376</v>
+      </c>
+      <c r="K38" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" t="s">
+        <v>27</v>
+      </c>
+      <c r="M38" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>401</v>
+      </c>
+      <c r="B39" t="s">
+        <v>393</v>
+      </c>
+      <c r="C39" t="s">
+        <v>387</v>
+      </c>
+      <c r="D39" t="s">
+        <v>411</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" t="s">
+        <v>377</v>
+      </c>
+      <c r="J39" t="s">
+        <v>376</v>
+      </c>
+      <c r="K39" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" t="s">
+        <v>27</v>
+      </c>
+      <c r="M39" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O39" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>402</v>
+      </c>
+      <c r="B40" t="s">
+        <v>394</v>
+      </c>
+      <c r="C40" t="s">
+        <v>387</v>
+      </c>
+      <c r="D40" t="s">
+        <v>412</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I40" t="s">
+        <v>377</v>
+      </c>
+      <c r="J40" t="s">
+        <v>376</v>
+      </c>
+      <c r="K40" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" t="s">
+        <v>27</v>
+      </c>
+      <c r="M40" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>403</v>
+      </c>
+      <c r="B41" t="s">
+        <v>395</v>
+      </c>
+      <c r="C41" t="s">
+        <v>387</v>
+      </c>
+      <c r="D41" t="s">
+        <v>413</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" t="s">
+        <v>377</v>
+      </c>
+      <c r="J41" t="s">
+        <v>376</v>
+      </c>
+      <c r="K41" t="s">
+        <v>13</v>
+      </c>
+      <c r="L41" t="s">
+        <v>27</v>
+      </c>
+      <c r="M41" t="s">
+        <v>21</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O41" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>404</v>
+      </c>
+      <c r="B42" t="s">
+        <v>396</v>
+      </c>
+      <c r="C42" t="s">
+        <v>387</v>
+      </c>
+      <c r="D42" t="s">
+        <v>414</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I42" t="s">
+        <v>377</v>
+      </c>
+      <c r="J42" t="s">
+        <v>376</v>
+      </c>
+      <c r="K42" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" t="s">
+        <v>27</v>
+      </c>
+      <c r="M42" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="O42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>405</v>
+      </c>
+      <c r="B43" t="s">
+        <v>441</v>
+      </c>
+      <c r="C43" t="s">
+        <v>442</v>
+      </c>
+      <c r="D43" t="s">
+        <v>443</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I43" t="s">
+        <v>176</v>
+      </c>
+      <c r="J43" t="s">
+        <v>299</v>
+      </c>
+      <c r="K43" t="s">
+        <v>13</v>
+      </c>
+      <c r="L43" t="s">
+        <v>27</v>
+      </c>
+      <c r="M43" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="O43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>454</v>
+      </c>
+      <c r="B44" t="s">
+        <v>451</v>
+      </c>
+      <c r="C44" t="s">
+        <v>442</v>
+      </c>
+      <c r="D44" t="s">
+        <v>452</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I44" t="s">
+        <v>176</v>
+      </c>
+      <c r="J44" t="s">
+        <v>299</v>
+      </c>
+      <c r="K44" t="s">
+        <v>13</v>
+      </c>
+      <c r="L44" t="s">
+        <v>27</v>
+      </c>
+      <c r="M44" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="O44" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>455</v>
+      </c>
+      <c r="B45" t="s">
+        <v>279</v>
+      </c>
+      <c r="C45" t="s">
+        <v>442</v>
+      </c>
+      <c r="D45" t="s">
+        <v>448</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I45" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" t="s">
+        <v>299</v>
+      </c>
+      <c r="K45" t="s">
+        <v>13</v>
+      </c>
+      <c r="L45" t="s">
+        <v>27</v>
+      </c>
+      <c r="M45" t="s">
+        <v>21</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="O45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>456</v>
+      </c>
+      <c r="B46" t="s">
+        <v>282</v>
+      </c>
+      <c r="C46" t="s">
+        <v>442</v>
+      </c>
+      <c r="D46" t="s">
+        <v>447</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I46" t="s">
+        <v>176</v>
+      </c>
+      <c r="J46" t="s">
+        <v>299</v>
+      </c>
+      <c r="K46" t="s">
+        <v>13</v>
+      </c>
+      <c r="L46" t="s">
+        <v>27</v>
+      </c>
+      <c r="M46" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="O46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>458</v>
+      </c>
+      <c r="B47" t="s">
+        <v>457</v>
+      </c>
+      <c r="C47" t="s">
+        <v>442</v>
+      </c>
+      <c r="D47" t="s">
+        <v>446</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="I47" t="s">
+        <v>176</v>
+      </c>
+      <c r="J47" t="s">
+        <v>299</v>
+      </c>
+      <c r="K47" t="s">
+        <v>13</v>
+      </c>
+      <c r="L47" t="s">
+        <v>27</v>
+      </c>
+      <c r="M47" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="O47" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4359,10 +5329,10 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>0</v>
